--- a/movies_db_uncleaned.xlsx
+++ b/movies_db_uncleaned.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Axiora User-28\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Axiora User-28\Downloads\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3FE9EC-99A9-441E-B720-610EE389FA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D804E07-6CFC-43C1-972D-1C5CBC55132D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="movie_actor" sheetId="4" r:id="rId4"/>
     <sheet name="languages" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="164">
   <si>
     <t>movie_id</t>
   </si>
@@ -385,9 +385,6 @@
     <t>Government of West Bengal</t>
   </si>
   <si>
-    <t>Column2</t>
-  </si>
-  <si>
     <t>K.G.F: Chapter 2</t>
   </si>
   <si>
@@ -506,13 +503,34 @@
   </si>
   <si>
     <t>language_name</t>
+  </si>
+  <si>
+    <t>budget mln</t>
+  </si>
+  <si>
+    <t>revenue mln</t>
+  </si>
+  <si>
+    <t>budget INR</t>
+  </si>
+  <si>
+    <t>revenue INR</t>
+  </si>
+  <si>
+    <t>TOTAL BUDGET</t>
+  </si>
+  <si>
+    <t>TOTAL REVENUE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_ [$₹-4009]\ * #,##0.00_ ;_ [$₹-4009]\ * \-#,##0.00_ ;_ [$₹-4009]\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -532,8 +550,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -543,6 +568,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -670,7 +707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -707,32 +744,49 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="52">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -740,6 +794,166 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right/>
         <top style="thin">
           <color indexed="64"/>
@@ -754,6 +968,595 @@
           <color indexed="64"/>
         </horizontal>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -797,361 +1600,10 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1163,35 +1615,6 @@
           <bgColor theme="9" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1248,38 +1671,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6A7FE39D-5614-4A7F-89B7-C167ABC0A251}" name="Movies" displayName="Movies" ref="A1:O40" totalsRowShown="0" headerRowDxfId="1" dataDxfId="25" headerRowBorderDxfId="17" tableBorderDxfId="18" totalsRowBorderDxfId="16">
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{5E453F0D-B27C-433C-BF11-BA3FE1A6822E}" name="movie_id" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{D24459DE-70F9-4ACC-99CD-AC5B1A7344CF}" name="title" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{A73DC6E7-A5B7-4D92-B13E-587CFA363BFA}" name="industry" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{DFE5EBBB-5DEF-4AB9-A5C9-802FC0AD1B5B}" name="release_year" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{D500D219-E618-40DD-B4AA-E390F996EF1E}" name="imdb_rating" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{D06057E5-53B4-474F-BA7C-D7BC731BE502}" name="studio" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{70C8CD53-1FFB-4649-B796-093E6560F8C9}" name="language_id" dataDxfId="9"/>
-    <tableColumn id="30" xr3:uid="{2A55675A-1700-4C12-807E-D551E62F4E62}" name="budget" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6A7FE39D-5614-4A7F-89B7-C167ABC0A251}" name="Movies" displayName="Movies" ref="A1:S40" headerRowDxfId="44" dataDxfId="43" headerRowBorderDxfId="41" tableBorderDxfId="42" totalsRowBorderDxfId="40">
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{5E453F0D-B27C-433C-BF11-BA3FE1A6822E}" name="movie_id" dataDxfId="38" totalsRowDxfId="39"/>
+    <tableColumn id="11" xr3:uid="{D24459DE-70F9-4ACC-99CD-AC5B1A7344CF}" name="title" dataDxfId="36" totalsRowDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{A73DC6E7-A5B7-4D92-B13E-587CFA363BFA}" name="industry" dataDxfId="34" totalsRowDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{DFE5EBBB-5DEF-4AB9-A5C9-802FC0AD1B5B}" name="release_year" dataDxfId="32" totalsRowDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{D500D219-E618-40DD-B4AA-E390F996EF1E}" name="imdb_rating" dataDxfId="30" totalsRowDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{D06057E5-53B4-474F-BA7C-D7BC731BE502}" name="studio" dataDxfId="28" totalsRowDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{70C8CD53-1FFB-4649-B796-093E6560F8C9}" name="language_id" dataDxfId="26" totalsRowDxfId="27"/>
+    <tableColumn id="30" xr3:uid="{2A55675A-1700-4C12-807E-D551E62F4E62}" name="budget" dataDxfId="24" totalsRowDxfId="25">
       <calculatedColumnFormula>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("budget",Financials[#Headers],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{5D2F4F68-D21C-4DB7-ADB8-C710579C0197}" name="revenue" dataDxfId="7">
+    <tableColumn id="31" xr3:uid="{5D2F4F68-D21C-4DB7-ADB8-C710579C0197}" name="revenue" dataDxfId="22" totalsRowDxfId="23">
       <calculatedColumnFormula>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("revenue",Financials[#Headers],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{49FDDDA2-6622-47F0-A5A4-AC052BE1B69C}" name="unit" dataDxfId="6">
+    <tableColumn id="32" xr3:uid="{49FDDDA2-6622-47F0-A5A4-AC052BE1B69C}" name="unit" dataDxfId="20" totalsRowDxfId="21">
       <calculatedColumnFormula>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("unit",Financials[#Headers],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{60C91868-B3EA-4024-91F4-072428473128}" name="currency" dataDxfId="5">
+    <tableColumn id="33" xr3:uid="{60C91868-B3EA-4024-91F4-072428473128}" name="currency" dataDxfId="18" totalsRowDxfId="19">
       <calculatedColumnFormula>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{CE7F218E-DD4C-4891-964D-422B492DEF66}" name="actor_id" dataDxfId="4">
+    <tableColumn id="36" xr3:uid="{CE7F218E-DD4C-4891-964D-422B492DEF66}" name="actor_id" dataDxfId="16" totalsRowDxfId="17">
       <calculatedColumnFormula>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{2D536834-3978-4C01-91A2-A4D4B9DA18CF}" name="name" dataDxfId="3">
+    <tableColumn id="37" xr3:uid="{2D536834-3978-4C01-91A2-A4D4B9DA18CF}" name="name" dataDxfId="14" totalsRowDxfId="15">
       <calculatedColumnFormula>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{A7B16292-565F-464E-92B7-22405818E0A8}" name="birth_year" dataDxfId="2">
+    <tableColumn id="38" xr3:uid="{A7B16292-565F-464E-92B7-22405818E0A8}" name="birth_year" dataDxfId="12" totalsRowDxfId="13">
       <calculatedColumnFormula>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{764C87DB-07AB-42B9-A852-8CF8913C6EF4}" name="language_name" dataDxfId="0">
+    <tableColumn id="39" xr3:uid="{764C87DB-07AB-42B9-A852-8CF8913C6EF4}" name="language_name" dataDxfId="10" totalsRowDxfId="11">
       <calculatedColumnFormula>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{2F627C35-0179-40F9-B0F8-964563B2F5AA}" name="budget mln" dataDxfId="8" totalsRowDxfId="9">
+      <calculatedColumnFormula>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{D8CA2E68-1A81-41FD-9695-41BDDB356510}" name="revenue mln" dataDxfId="6" totalsRowDxfId="7">
+      <calculatedColumnFormula>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{0CF952DD-B97E-44EB-B308-0646C8A25B78}" name="budget INR" dataDxfId="4" totalsRowDxfId="5">
+      <calculatedColumnFormula>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{295FE231-CAD2-4E8C-B740-105798D27EF6}" name="revenue INR" dataDxfId="2" totalsRowDxfId="3">
+      <calculatedColumnFormula>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1287,7 +1722,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEC907F-917F-4689-8EAB-F7CEF660B9E4}" name="Financials" displayName="Financials" ref="A1:E41" totalsRowShown="0" headerRowDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DCEC907F-917F-4689-8EAB-F7CEF660B9E4}" name="Financials" displayName="Financials" ref="A1:E41" totalsRowShown="0" headerRowDxfId="51">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{D1A9B0F4-FC15-4DC9-80C7-7EBF56996521}" name="movie_id"/>
     <tableColumn id="2" xr3:uid="{7A82C7E9-BE81-4BFD-9DE1-91C9F01BD827}" name="budget"/>
@@ -1300,7 +1735,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{49E9627B-7F83-4E00-A9BD-B2B85ADBBA2F}" name="actors" displayName="actors" ref="A1:C68" totalsRowShown="0" headerRowDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{49E9627B-7F83-4E00-A9BD-B2B85ADBBA2F}" name="actors" displayName="actors" ref="A1:C68" totalsRowShown="0" headerRowDxfId="50">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{17C41506-36D4-4294-9829-5A0C52DE3455}" name="actor_id"/>
     <tableColumn id="2" xr3:uid="{2876D79C-DCCC-46A7-9A7C-E9583B5ED0CC}" name="name"/>
@@ -1311,7 +1746,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{69F3DFB9-F7AC-4F5D-9639-8E5EFD749C75}" name="movieactor" displayName="movieactor" ref="A1:B86" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{69F3DFB9-F7AC-4F5D-9639-8E5EFD749C75}" name="movieactor" displayName="movieactor" ref="A1:B86" totalsRowShown="0" headerRowDxfId="49">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{726AA249-607F-4CEE-9C80-419BD67B7D42}" name="movie_id"/>
     <tableColumn id="2" xr3:uid="{A11280A0-C25A-482F-B3E4-13975B2F5282}" name="actor_id"/>
@@ -1321,10 +1756,10 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1C058435-0457-4C21-A779-EC166EB5551A}" name="languages" displayName="languages" ref="A1:B9" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1C058435-0457-4C21-A779-EC166EB5551A}" name="languages" displayName="languages" ref="A1:B9" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E256DBAD-6FC6-4A32-8A1D-C74A5F599F74}" name="language_id" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{583CF6B9-244C-4D0F-A271-B5A1C600F170}" name="language_name" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{E256DBAD-6FC6-4A32-8A1D-C74A5F599F74}" name="language_id" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{583CF6B9-244C-4D0F-A271-B5A1C600F170}" name="language_name" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1593,7 +2028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.453125" bestFit="1" customWidth="1"/>
@@ -1611,9 +2046,13 @@
     <col min="13" max="13" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1657,15 +2096,27 @@
         <v>37</v>
       </c>
       <c r="O1" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="P1" s="8" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q1" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="10">
         <v>101</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
@@ -1698,29 +2149,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>50</v>
       </c>
-      <c r="M2" s="14" t="str">
+      <c r="M2" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Yash</v>
       </c>
-      <c r="N2" s="17">
+      <c r="N2" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1986</v>
       </c>
-      <c r="O2" s="18" t="str">
+      <c r="O2" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Kannada</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P2" s="17">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>1000</v>
+      </c>
+      <c r="Q2" s="17">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>12500</v>
+      </c>
+      <c r="R2" s="17">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>1000</v>
+      </c>
+      <c r="S2" s="17">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>102</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>7</v>
@@ -1753,29 +2220,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>52</v>
       </c>
-      <c r="M3" s="14" t="str">
+      <c r="M3" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Benedict Cumberbatch</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1976</v>
       </c>
-      <c r="O3" s="18" t="str">
+      <c r="O3" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P3" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>200</v>
+      </c>
+      <c r="Q3" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>954.8</v>
+      </c>
+      <c r="R3" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>18400</v>
+      </c>
+      <c r="S3" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>87841.599999999991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>103</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>7</v>
@@ -1808,29 +2291,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>54</v>
       </c>
-      <c r="M4" s="14" t="str">
+      <c r="M4" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Chris Hemsworth</v>
       </c>
-      <c r="N4" s="17">
+      <c r="N4" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1983</v>
       </c>
-      <c r="O4" s="18" t="str">
+      <c r="O4" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P4" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>165</v>
+      </c>
+      <c r="Q4" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>644.79999999999995</v>
+      </c>
+      <c r="R4" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>15180</v>
+      </c>
+      <c r="S4" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>59321.599999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>104</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>7</v>
@@ -1863,29 +2362,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>54</v>
       </c>
-      <c r="M5" s="14" t="str">
+      <c r="M5" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Chris Hemsworth</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1983</v>
       </c>
-      <c r="O5" s="18" t="str">
+      <c r="O5" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P5" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>180</v>
+      </c>
+      <c r="Q5" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>854</v>
+      </c>
+      <c r="R5" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>16560</v>
+      </c>
+      <c r="S5" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>78568</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>7</v>
@@ -1918,29 +2433,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>54</v>
       </c>
-      <c r="M6" s="14" t="str">
+      <c r="M6" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Chris Hemsworth</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1983</v>
       </c>
-      <c r="O6" s="18" t="str">
+      <c r="O6" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P6" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>250</v>
+      </c>
+      <c r="Q6" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>670</v>
+      </c>
+      <c r="R6" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>23000</v>
+      </c>
+      <c r="S6" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>61640</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>106</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>6</v>
@@ -1973,29 +2504,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>57</v>
       </c>
-      <c r="M7" s="14" t="str">
+      <c r="M7" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Amitabh Bachchan</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1942</v>
       </c>
-      <c r="O7" s="18" t="str">
+      <c r="O7" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P7" s="4" t="e">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q7" s="4" t="e">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="R7" s="4" t="e">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="S7" s="4" t="e">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>107</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>6</v>
@@ -2028,29 +2575,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>59</v>
       </c>
-      <c r="M8" s="14" t="str">
+      <c r="M8" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Shah Rukh Khan</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O8" s="18" t="str">
+      <c r="O8" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P8" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>400</v>
+      </c>
+      <c r="Q8" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>2000</v>
+      </c>
+      <c r="R8" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>400</v>
+      </c>
+      <c r="S8" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>108</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>6</v>
@@ -2083,29 +2646,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>61</v>
       </c>
-      <c r="M9" s="14" t="str">
+      <c r="M9" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Aamir Khan</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O9" s="18" t="str">
+      <c r="O9" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P9" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>550</v>
+      </c>
+      <c r="Q9" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>4000</v>
+      </c>
+      <c r="R9" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>550</v>
+      </c>
+      <c r="S9" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>109</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>6</v>
@@ -2138,29 +2717,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>59</v>
       </c>
-      <c r="M10" s="14" t="str">
+      <c r="M10" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Shah Rukh Khan</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O10" s="18" t="str">
+      <c r="O10" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P10" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>390</v>
+      </c>
+      <c r="Q10" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>1360</v>
+      </c>
+      <c r="R10" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>390</v>
+      </c>
+      <c r="S10" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>110</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>6</v>
@@ -2193,29 +2788,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>65</v>
       </c>
-      <c r="M11" s="14" t="str">
+      <c r="M11" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Ranveer Singh</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1985</v>
       </c>
-      <c r="O11" s="18" t="str">
+      <c r="O11" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P11" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>1400</v>
+      </c>
+      <c r="Q11" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>3500</v>
+      </c>
+      <c r="R11" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>1400</v>
+      </c>
+      <c r="S11" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>111</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>7</v>
@@ -2248,29 +2859,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>67</v>
       </c>
-      <c r="M12" s="14" t="str">
+      <c r="M12" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Tim Robbins</v>
       </c>
-      <c r="N12" s="17">
+      <c r="N12" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1958</v>
       </c>
-      <c r="O12" s="18" t="str">
+      <c r="O12" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P12" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>25</v>
+      </c>
+      <c r="Q12" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>73.3</v>
+      </c>
+      <c r="R12" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>2300</v>
+      </c>
+      <c r="S12" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>6743.5999999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>112</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>7</v>
@@ -2303,29 +2930,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>69</v>
       </c>
-      <c r="M13" s="14" t="str">
+      <c r="M13" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Leonardo DiCaprio</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1974</v>
       </c>
-      <c r="O13" s="18" t="str">
+      <c r="O13" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P13" s="4" t="e">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q13" s="4" t="e">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="R13" s="4" t="e">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>#N/A</v>
+      </c>
+      <c r="S13" s="4" t="e">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>113</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>7</v>
@@ -2358,29 +3001,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>71</v>
       </c>
-      <c r="M14" s="14" t="str">
+      <c r="M14" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Matthew McConaughey</v>
       </c>
-      <c r="N14" s="17">
+      <c r="N14" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1969</v>
       </c>
-      <c r="O14" s="18" t="str">
+      <c r="O14" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P14" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>165</v>
+      </c>
+      <c r="Q14" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>701.8</v>
+      </c>
+      <c r="R14" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>15180</v>
+      </c>
+      <c r="S14" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>64565.599999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>115</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>7</v>
@@ -2413,29 +3072,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>75</v>
       </c>
-      <c r="M15" s="14" t="str">
+      <c r="M15" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Will Smith</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1968</v>
       </c>
-      <c r="O15" s="18" t="str">
+      <c r="O15" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P15" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>55</v>
+      </c>
+      <c r="Q15" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>307.10000000000002</v>
+      </c>
+      <c r="R15" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>5060</v>
+      </c>
+      <c r="S15" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>28253.200000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>116</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>7</v>
@@ -2468,29 +3143,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>77</v>
       </c>
-      <c r="M16" s="14" t="str">
+      <c r="M16" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Russell Crowe</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1964</v>
       </c>
-      <c r="O16" s="18" t="str">
+      <c r="O16" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P16" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>103</v>
+      </c>
+      <c r="Q16" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>460.5</v>
+      </c>
+      <c r="R16" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>9476</v>
+      </c>
+      <c r="S16" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>42366</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>117</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>7</v>
@@ -2523,29 +3214,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>69</v>
       </c>
-      <c r="M17" s="14" t="str">
+      <c r="M17" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Leonardo DiCaprio</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1974</v>
       </c>
-      <c r="O17" s="18" t="str">
+      <c r="O17" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P17" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>200</v>
+      </c>
+      <c r="Q17" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>2202</v>
+      </c>
+      <c r="R17" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>18400</v>
+      </c>
+      <c r="S17" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>202584</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>118</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>7</v>
@@ -2578,29 +3285,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>80</v>
       </c>
-      <c r="M18" s="14" t="str">
+      <c r="M18" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>James Stewart</v>
       </c>
-      <c r="N18" s="17">
+      <c r="N18" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1908</v>
       </c>
-      <c r="O18" s="18" t="str">
+      <c r="O18" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P18" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>3.18</v>
+      </c>
+      <c r="Q18" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>3.3</v>
+      </c>
+      <c r="R18" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>292.56</v>
+      </c>
+      <c r="S18" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>303.59999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>119</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>7</v>
@@ -2633,29 +3356,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>82</v>
       </c>
-      <c r="M19" s="14" t="str">
+      <c r="M19" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Sam Worthington</v>
       </c>
-      <c r="N19" s="17">
+      <c r="N19" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1976</v>
       </c>
-      <c r="O19" s="18" t="str">
+      <c r="O19" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P19" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>237</v>
+      </c>
+      <c r="Q19" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>2847</v>
+      </c>
+      <c r="R19" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>21804</v>
+      </c>
+      <c r="S19" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>261924</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>120</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>7</v>
@@ -2688,29 +3427,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>84</v>
       </c>
-      <c r="M20" s="14" t="str">
+      <c r="M20" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Marlon Brando</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1924</v>
       </c>
-      <c r="O20" s="18" t="str">
+      <c r="O20" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P20" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>7.2</v>
+      </c>
+      <c r="Q20" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>291</v>
+      </c>
+      <c r="R20" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>662.4</v>
+      </c>
+      <c r="S20" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>26772</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>121</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>7</v>
@@ -2743,29 +3498,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L21" s="14">
+      <c r="L21" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>86</v>
       </c>
-      <c r="M21" s="14" t="str">
+      <c r="M21" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Christian Bale</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1974</v>
       </c>
-      <c r="O21" s="18" t="str">
+      <c r="O21" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P21" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>185</v>
+      </c>
+      <c r="Q21" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>1006</v>
+      </c>
+      <c r="R21" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>17020</v>
+      </c>
+      <c r="S21" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>92552</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>122</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>7</v>
@@ -2798,29 +3569,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>88</v>
       </c>
-      <c r="M22" s="14" t="str">
+      <c r="M22" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Liam Neeson</v>
       </c>
-      <c r="N22" s="17">
+      <c r="N22" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1952</v>
       </c>
-      <c r="O22" s="18" t="str">
+      <c r="O22" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P22" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>22</v>
+      </c>
+      <c r="Q22" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>322.2</v>
+      </c>
+      <c r="R22" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>2024</v>
+      </c>
+      <c r="S22" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>29642.399999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>123</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>7</v>
@@ -2853,29 +3640,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>90</v>
       </c>
-      <c r="M23" s="14" t="str">
+      <c r="M23" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Sam Neill</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1947</v>
       </c>
-      <c r="O23" s="18" t="str">
+      <c r="O23" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P23" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>63</v>
+      </c>
+      <c r="Q23" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>1046</v>
+      </c>
+      <c r="R23" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>5796</v>
+      </c>
+      <c r="S23" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>96232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>124</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>7</v>
@@ -2908,29 +3711,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L24" s="14">
+      <c r="L24" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>92</v>
       </c>
-      <c r="M24" s="14" t="str">
+      <c r="M24" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Song Kang-ho</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N24" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1967</v>
       </c>
-      <c r="O24" s="18" t="str">
+      <c r="O24" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P24" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>15.5</v>
+      </c>
+      <c r="Q24" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>263.10000000000002</v>
+      </c>
+      <c r="R24" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>1426</v>
+      </c>
+      <c r="S24" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>24205.200000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>125</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>7</v>
@@ -2963,29 +3782,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L25" s="14">
+      <c r="L25" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>94</v>
       </c>
-      <c r="M25" s="14" t="str">
+      <c r="M25" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Robert Downey Jr.</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O25" s="18" t="str">
+      <c r="O25" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P25" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>400</v>
+      </c>
+      <c r="Q25" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>2798</v>
+      </c>
+      <c r="R25" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>36800</v>
+      </c>
+      <c r="S25" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>257416</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>126</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>7</v>
@@ -3018,29 +3853,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L26" s="14">
+      <c r="L26" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>94</v>
       </c>
-      <c r="M26" s="14" t="str">
+      <c r="M26" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Robert Downey Jr.</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O26" s="18" t="str">
+      <c r="O26" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P26" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>400</v>
+      </c>
+      <c r="Q26" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>2048</v>
+      </c>
+      <c r="R26" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>36800</v>
+      </c>
+      <c r="S26" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>188416</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>127</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>6</v>
@@ -3073,29 +3924,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>150</v>
       </c>
-      <c r="M27" s="14" t="str">
+      <c r="M27" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Kanu Banerjee</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1905</v>
       </c>
-      <c r="O27" s="18" t="str">
+      <c r="O27" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Bengali</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P27" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>70</v>
+      </c>
+      <c r="Q27" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>100</v>
+      </c>
+      <c r="R27" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>70</v>
+      </c>
+      <c r="S27" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>128</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>6</v>
@@ -3128,29 +3995,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>61</v>
       </c>
-      <c r="M28" s="14" t="str">
+      <c r="M28" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Aamir Khan</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O28" s="18" t="str">
+      <c r="O28" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P28" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>120</v>
+      </c>
+      <c r="Q28" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>1350</v>
+      </c>
+      <c r="R28" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>120</v>
+      </c>
+      <c r="S28" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>129</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>6</v>
@@ -3183,29 +4066,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>51</v>
       </c>
-      <c r="M29" s="14" t="str">
+      <c r="M29" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Sanjay Dutt</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1959</v>
       </c>
-      <c r="O29" s="18" t="str">
+      <c r="O29" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P29" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>100</v>
+      </c>
+      <c r="Q29" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>410</v>
+      </c>
+      <c r="R29" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>100</v>
+      </c>
+      <c r="S29" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>130</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>6</v>
@@ -3238,29 +4137,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>61</v>
       </c>
-      <c r="M30" s="14" t="str">
+      <c r="M30" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Aamir Khan</v>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O30" s="18" t="str">
+      <c r="O30" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P30" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>850</v>
+      </c>
+      <c r="Q30" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>8540</v>
+      </c>
+      <c r="R30" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>850</v>
+      </c>
+      <c r="S30" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>8540</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>131</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>6</v>
@@ -3293,29 +4208,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>155</v>
       </c>
-      <c r="M31" s="14" t="str">
+      <c r="M31" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Ranbir Kapoor</v>
       </c>
-      <c r="N31" s="17">
+      <c r="N31" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1982</v>
       </c>
-      <c r="O31" s="18" t="str">
+      <c r="O31" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P31" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>1000</v>
+      </c>
+      <c r="Q31" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>5900</v>
+      </c>
+      <c r="R31" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>1000</v>
+      </c>
+      <c r="S31" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>132</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>6</v>
@@ -3348,29 +4279,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L32" s="14">
+      <c r="L32" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>156</v>
       </c>
-      <c r="M32" s="14" t="str">
+      <c r="M32" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Allu Arjun</v>
       </c>
-      <c r="N32" s="17">
+      <c r="N32" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1982</v>
       </c>
-      <c r="O32" s="18" t="str">
+      <c r="O32" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Telugu</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P32" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>2000</v>
+      </c>
+      <c r="Q32" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>3600</v>
+      </c>
+      <c r="R32" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>2000</v>
+      </c>
+      <c r="S32" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>133</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>6</v>
@@ -3403,29 +4350,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>158</v>
       </c>
-      <c r="M33" s="14" t="str">
+      <c r="M33" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>N. T. Rama Rao Jr.</v>
       </c>
-      <c r="N33" s="17">
+      <c r="N33" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1983</v>
       </c>
-      <c r="O33" s="18" t="str">
+      <c r="O33" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Telugu</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P33" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>5500</v>
+      </c>
+      <c r="Q33" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>12000</v>
+      </c>
+      <c r="R33" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>5500</v>
+      </c>
+      <c r="S33" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>134</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>6</v>
@@ -3458,29 +4421,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>160</v>
       </c>
-      <c r="M34" s="14" t="str">
+      <c r="M34" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Prabhas</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1979</v>
       </c>
-      <c r="O34" s="18" t="str">
+      <c r="O34" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Telugu</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P34" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>1800</v>
+      </c>
+      <c r="Q34" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>6500</v>
+      </c>
+      <c r="R34" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>1800</v>
+      </c>
+      <c r="S34" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>135</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>6</v>
@@ -3513,29 +4492,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L35" s="14">
+      <c r="L35" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>162</v>
       </c>
-      <c r="M35" s="14" t="str">
+      <c r="M35" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Mithun Chakraborty</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N35" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1950</v>
       </c>
-      <c r="O35" s="18" t="str">
+      <c r="O35" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P35" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>250</v>
+      </c>
+      <c r="Q35" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>3409</v>
+      </c>
+      <c r="R35" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>250</v>
+      </c>
+      <c r="S35" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>3409</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>136</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>6</v>
@@ -3568,29 +4563,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L36" s="14">
+      <c r="L36" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>164</v>
       </c>
-      <c r="M36" s="14" t="str">
+      <c r="M36" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Salman Khan</v>
       </c>
-      <c r="N36" s="17">
+      <c r="N36" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O36" s="18" t="str">
+      <c r="O36" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P36" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>900</v>
+      </c>
+      <c r="Q36" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>11690</v>
+      </c>
+      <c r="R36" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>900</v>
+      </c>
+      <c r="S36" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>11690</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>137</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>7</v>
@@ -3623,29 +4634,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L37" s="14">
+      <c r="L37" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>95</v>
       </c>
-      <c r="M37" s="14" t="str">
+      <c r="M37" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Chris Evans</v>
       </c>
-      <c r="N37" s="17">
+      <c r="N37" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1981</v>
       </c>
-      <c r="O37" s="18" t="str">
+      <c r="O37" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P37" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>216.7</v>
+      </c>
+      <c r="Q37" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>370.6</v>
+      </c>
+      <c r="R37" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>19936.399999999998</v>
+      </c>
+      <c r="S37" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>34095.200000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>138</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>7</v>
@@ -3678,29 +4705,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>USD</v>
       </c>
-      <c r="L38" s="14">
+      <c r="L38" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>95</v>
       </c>
-      <c r="M38" s="14" t="str">
+      <c r="M38" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Chris Evans</v>
       </c>
-      <c r="N38" s="17">
+      <c r="N38" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1981</v>
       </c>
-      <c r="O38" s="18" t="str">
+      <c r="O38" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>English</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P38" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>177</v>
+      </c>
+      <c r="Q38" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>714.4</v>
+      </c>
+      <c r="R38" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>16284</v>
+      </c>
+      <c r="S38" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>65724.800000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>139</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>6</v>
@@ -3733,29 +4776,45 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="4">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>164</v>
       </c>
-      <c r="M39" s="14" t="str">
+      <c r="M39" s="4" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Salman Khan</v>
       </c>
-      <c r="N39" s="17">
+      <c r="N39" s="4">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1965</v>
       </c>
-      <c r="O39" s="18" t="str">
+      <c r="O39" s="15" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P39" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>1800</v>
+      </c>
+      <c r="Q39" s="4">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>3100</v>
+      </c>
+      <c r="R39" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>1800</v>
+      </c>
+      <c r="S39" s="4">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="11">
         <v>140</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>6</v>
@@ -3788,30 +4847,64 @@
         <f>INDEX(financials!A:E,MATCH(Movies[[#This Row],[movie_id]],Financials[[#All],[movie_id]],0),MATCH("currency",Financials[#Headers],0))</f>
         <v>INR</v>
       </c>
-      <c r="L40" s="15">
+      <c r="L40" s="5">
         <f>INDEX(movie_actor!A:B,MATCH(Movies[[#This Row],[movie_id]],movie_actor!A:A,0),MATCH("actor_id",movieactor[#Headers],0))</f>
         <v>169</v>
       </c>
-      <c r="M40" s="15" t="str">
+      <c r="M40" s="5" t="str">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("name",actors[#Headers],0))</f>
         <v>Sidharth Malhotra</v>
       </c>
-      <c r="N40" s="19">
+      <c r="N40" s="5">
         <f>INDEX(actors!A:C,MATCH(Movies[[#This Row],[actor_id]],actors[[#All],[actor_id]],0),MATCH("birth_year",actors[#Headers],0))</f>
         <v>1985</v>
       </c>
-      <c r="O40" s="20" t="str">
+      <c r="O40" s="16" t="str">
         <f>INDEX(languages!A:B,MATCH(Movies[[#This Row],[language_id]],languages!A:A,0),MATCH("language_name",languages[#Headers],0))</f>
         <v>Hindi</v>
+      </c>
+      <c r="P40" s="5">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[budget]]*1000,Movies[[#This Row],[budget]])</f>
+        <v>500</v>
+      </c>
+      <c r="Q40" s="5">
+        <f>IF(Movies[[#This Row],[unit]]="Billions",Movies[[#This Row],[revenue]]*1000,Movies[[#This Row],[revenue]])</f>
+        <v>950</v>
+      </c>
+      <c r="R40" s="5">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[budget mln]]*92,Movies[[#This Row],[budget mln]])</f>
+        <v>500</v>
+      </c>
+      <c r="S40" s="5">
+        <f>IF(Movies[[#This Row],[currency]]="USD",Movies[[#This Row],[revenue mln]]*92,Movies[[#This Row],[revenue mln]])</f>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="R42" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="S42" s="18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="R43" s="19">
+        <f>SUMIF(Movies[budget INR],"&lt;&gt;#N/A")</f>
+        <v>301031.36</v>
+      </c>
+      <c r="S43" s="19">
+        <f>SUMIF(Movies[revenue INR],"&lt;&gt;#N/A")</f>
+        <v>1790075.7999999998</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B40">
-    <cfRule type="duplicateValues" dxfId="23" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -6014,11 +7107,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>158</v>
+      <c r="B1" s="14" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -6094,34 +7187,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="46297aa2-77d1-4586-9726-07d56a535ee7" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="631564f6-0349-4cc5-b00d-7cf3ba42f824">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MediaLengthInSeconds xmlns="631564f6-0349-4cc5-b00d-7cf3ba42f824" xsi:nil="true"/>
-    <SharedWithUsers xmlns="46297aa2-77d1-4586-9726-07d56a535ee7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100686C0266E115364AA9B96DE5BECF7DB6" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c921848065db5a49d1de2391ec81580e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="631564f6-0349-4cc5-b00d-7cf3ba42f824" xmlns:ns3="46297aa2-77d1-4586-9726-07d56a535ee7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff9dd1b7eff9d7fccc1b7fb333026bb0" ns2:_="" ns3:_="">
     <xsd:import namespace="631564f6-0349-4cc5-b00d-7cf3ba42f824"/>
@@ -6350,26 +7415,35 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEFF9027-FBEF-4910-8EE6-13D64012C7E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="46297aa2-77d1-4586-9726-07d56a535ee7"/>
-    <ds:schemaRef ds:uri="631564f6-0349-4cc5-b00d-7cf3ba42f824"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C97D6F-A515-40FC-959A-7BC863F10CEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="46297aa2-77d1-4586-9726-07d56a535ee7" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="631564f6-0349-4cc5-b00d-7cf3ba42f824">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MediaLengthInSeconds xmlns="631564f6-0349-4cc5-b00d-7cf3ba42f824" xsi:nil="true"/>
+    <SharedWithUsers xmlns="46297aa2-77d1-4586-9726-07d56a535ee7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02BA008F-2FD2-4901-8027-A024DA31C6C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6386,4 +7460,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C97D6F-A515-40FC-959A-7BC863F10CEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEFF9027-FBEF-4910-8EE6-13D64012C7E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="46297aa2-77d1-4586-9726-07d56a535ee7"/>
+    <ds:schemaRef ds:uri="631564f6-0349-4cc5-b00d-7cf3ba42f824"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>